--- a/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0003T0006Z000C1N46_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0003T0006Z000C1N46_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>37.729131461986</v>
+        <v>6.130983862572725</v>
       </c>
       <c r="D2" t="n">
-        <v>37.35686252725398</v>
+        <v>6.070490160678772</v>
       </c>
       <c r="E2" t="n">
-        <v>9.786817290141991</v>
+        <v>1.590357809648073</v>
       </c>
       <c r="F2" t="n">
-        <v>9.683251004145051</v>
+        <v>1.573528288173571</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>31.33886464452811</v>
+        <v>5.092565504735818</v>
       </c>
       <c r="D3" t="n">
-        <v>31.06864607778529</v>
+        <v>5.04865498764011</v>
       </c>
       <c r="E3" t="n">
-        <v>9.786817290141991</v>
+        <v>1.590357809648073</v>
       </c>
       <c r="F3" t="n">
-        <v>9.683251004145051</v>
+        <v>1.573528288173571</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>29.53292178230021</v>
+        <v>4.799099789623784</v>
       </c>
       <c r="D4" t="n">
-        <v>28.93821838069716</v>
+        <v>4.702460486863289</v>
       </c>
       <c r="E4" t="n">
-        <v>9.786817290141991</v>
+        <v>1.590357809648073</v>
       </c>
       <c r="F4" t="n">
-        <v>9.683251004145051</v>
+        <v>1.573528288173571</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>30.5795145457007</v>
+        <v>4.969171113676365</v>
       </c>
       <c r="D5" t="n">
-        <v>29.82089648365982</v>
+        <v>4.845895678594721</v>
       </c>
       <c r="E5" t="n">
-        <v>9.786817290141991</v>
+        <v>1.590357809648073</v>
       </c>
       <c r="F5" t="n">
-        <v>9.683251004145051</v>
+        <v>1.573528288173571</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>38.39299087141048</v>
+        <v>6.238861016604203</v>
       </c>
       <c r="D6" t="n">
-        <v>38.25245750381022</v>
+        <v>6.216024344369161</v>
       </c>
       <c r="E6" t="n">
-        <v>9.786817290141991</v>
+        <v>1.590357809648073</v>
       </c>
       <c r="F6" t="n">
-        <v>9.683251004145051</v>
+        <v>1.573528288173571</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>26.7273057809839</v>
+        <v>4.343187189409885</v>
       </c>
       <c r="D7" t="n">
-        <v>26.07011225272195</v>
+        <v>4.236393241067317</v>
       </c>
       <c r="E7" t="n">
-        <v>9.786817290141991</v>
+        <v>1.590357809648073</v>
       </c>
       <c r="F7" t="n">
-        <v>9.683251004145051</v>
+        <v>1.573528288173571</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>27.84213912046192</v>
+        <v>4.524347607075063</v>
       </c>
       <c r="D8" t="n">
-        <v>28.38399734304794</v>
+        <v>4.61239956824529</v>
       </c>
       <c r="E8" t="n">
-        <v>9.786817290141991</v>
+        <v>1.590357809648073</v>
       </c>
       <c r="F8" t="n">
-        <v>9.683251004145051</v>
+        <v>1.573528288173571</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>31.72564666076002</v>
+        <v>5.155417582373504</v>
       </c>
       <c r="D9" t="n">
-        <v>31.63265048568707</v>
+        <v>5.140305703924148</v>
       </c>
       <c r="E9" t="n">
-        <v>9.786817290141991</v>
+        <v>1.590357809648073</v>
       </c>
       <c r="F9" t="n">
-        <v>9.683251004145051</v>
+        <v>1.573528288173571</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>28.42199490160328</v>
+        <v>4.618574171510533</v>
       </c>
       <c r="D10" t="n">
-        <v>28.57852333779429</v>
+        <v>4.644010042391573</v>
       </c>
       <c r="E10" t="n">
-        <v>9.786817290141991</v>
+        <v>1.590357809648073</v>
       </c>
       <c r="F10" t="n">
-        <v>9.683251004145051</v>
+        <v>1.573528288173571</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>27.48347541084843</v>
+        <v>4.46606475426287</v>
       </c>
       <c r="D11" t="n">
-        <v>28.21631669018459</v>
+        <v>4.585151462154996</v>
       </c>
       <c r="E11" t="n">
-        <v>9.786817290141991</v>
+        <v>1.590357809648073</v>
       </c>
       <c r="F11" t="n">
-        <v>9.683251004145051</v>
+        <v>1.573528288173571</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>25.2453165066684</v>
+        <v>4.102363932333614</v>
       </c>
       <c r="D12" t="n">
-        <v>25.65188322835555</v>
+        <v>4.168431024607777</v>
       </c>
       <c r="E12" t="n">
-        <v>9.786817290141991</v>
+        <v>1.590357809648073</v>
       </c>
       <c r="F12" t="n">
-        <v>9.683251004145051</v>
+        <v>1.573528288173571</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>8.587285711699833</v>
+        <v>1.395433928151223</v>
       </c>
       <c r="D13" t="n">
-        <v>8.549745381006293</v>
+        <v>1.389333624413523</v>
       </c>
       <c r="E13" t="n">
-        <v>9.786817290141991</v>
+        <v>1.590357809648073</v>
       </c>
       <c r="F13" t="n">
-        <v>9.683251004145051</v>
+        <v>1.573528288173571</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>3.007549970346201</v>
+        <v>0.4887268701812577</v>
       </c>
       <c r="D14" t="n">
-        <v>3.393566871685679</v>
+        <v>0.5514546166489228</v>
       </c>
       <c r="E14" t="n">
-        <v>9.786817290141991</v>
+        <v>1.590357809648073</v>
       </c>
       <c r="F14" t="n">
-        <v>9.683251004145051</v>
+        <v>1.573528288173571</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>11.26714694733875</v>
+        <v>1.830911378942547</v>
       </c>
       <c r="D15" t="n">
-        <v>10.96882585480209</v>
+        <v>1.782434201405339</v>
       </c>
       <c r="E15" t="n">
-        <v>9.786817290141991</v>
+        <v>1.590357809648073</v>
       </c>
       <c r="F15" t="n">
-        <v>9.683251004145051</v>
+        <v>1.573528288173571</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>15.72907559747086</v>
+        <v>2.555974784589015</v>
       </c>
       <c r="D16" t="n">
-        <v>16.04942002255765</v>
+        <v>2.608030753665619</v>
       </c>
       <c r="E16" t="n">
-        <v>9.786817290141991</v>
+        <v>1.590357809648073</v>
       </c>
       <c r="F16" t="n">
-        <v>9.683251004145051</v>
+        <v>1.573528288173571</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>18.48837126260932</v>
+        <v>3.004360330174015</v>
       </c>
       <c r="D17" t="n">
-        <v>18.32870481280746</v>
+        <v>2.978414532081211</v>
       </c>
       <c r="E17" t="n">
-        <v>9.786817290141991</v>
+        <v>1.590357809648073</v>
       </c>
       <c r="F17" t="n">
-        <v>9.683251004145051</v>
+        <v>1.573528288173571</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>32.13033552138871</v>
+        <v>5.221179522225666</v>
       </c>
       <c r="D18" t="n">
-        <v>32.15223686065386</v>
+        <v>5.224738489856252</v>
       </c>
       <c r="E18" t="n">
-        <v>9.786817290141991</v>
+        <v>1.590357809648073</v>
       </c>
       <c r="F18" t="n">
-        <v>9.683251004145051</v>
+        <v>1.573528288173571</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
